--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/ConditionalFormattingOrder/ConditionalFormattingOrder.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/ConditionalFormattingOrder/ConditionalFormattingOrder.xlsx
@@ -378,14 +378,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
-  <x:sheetPr>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
-  </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <x:sheetData>
     <x:row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <x:c r="A1" s="0">
+      <x:c r="A1">
         <x:v>10</x:v>
       </x:c>
     </x:row>
@@ -402,10 +399,7 @@
       <x:formula>0</x:formula>
     </x:cfRule>
   </x:conditionalFormatting>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:pageSetup paperSize="9" scale="100" pageOrder="downThenOver" orientation="portrait" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" r:id="rId1"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </x:worksheet>
 </file>
--- a/XLibur.Tests/Resource/Other/StyleReferenceFiles/ConditionalFormattingOrder/ConditionalFormattingOrder.xlsx
+++ b/XLibur.Tests/Resource/Other/StyleReferenceFiles/ConditionalFormattingOrder/ConditionalFormattingOrder.xlsx
@@ -388,7 +388,7 @@
     </x:row>
   </x:sheetData>
   <x:phoneticPr fontId="1" type="noConversion"/>
-  <x:conditionalFormatting sqref="A1:A1">
+  <x:conditionalFormatting sqref="A1">
     <x:cfRule type="cellIs" dxfId="0" priority="1" stopIfTrue="1" operator="greaterThan">
       <x:formula>5</x:formula>
     </x:cfRule>
